--- a/excel/Buku_Kolam_Mitra_Twenty_Swim.xlsx
+++ b/excel/Buku_Kolam_Mitra_Twenty_Swim.xlsx
@@ -3063,16 +3063,16 @@
           <t>Data kolam + info internal kerjasama. Sel kuning = ada catatan keluhan. Sel abu-abu muda = kolom yang masih perlu dilengkapi. Kolom dropdown tinggal pilih.</t>
         </is>
       </c>
-      <c r="L2" s="41" t="inlineStr">
+      <c r="M2" s="41" t="inlineStr">
         <is>
           <t>Terisi:</t>
         </is>
       </c>
-      <c r="M2" s="42">
+      <c r="N2" s="42">
         <f>COUNTA($B$5:$B$404)</f>
         <v/>
       </c>
-      <c r="N2" s="40" t="inlineStr">
+      <c r="O2" s="40" t="inlineStr">
         <is>
           <t>kolam</t>
         </is>
@@ -12251,11 +12251,11 @@
     <dataValidation sqref="K5:K404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pilihan tidak valid" error="Silakan pilih dari daftar dropdown." type="list">
       <formula1>=Daftar!$I$2:$I$3</formula1>
     </dataValidation>
+    <dataValidation sqref="O5:O404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pilihan tidak valid" error="Silakan pilih dari daftar dropdown." type="list">
+      <formula1>=Daftar!$M$2:$M$3</formula1>
+    </dataValidation>
     <dataValidation sqref="M5:M404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pilihan tidak valid" error="Silakan pilih dari daftar dropdown." type="list">
       <formula1>=Daftar!$K$2:$K$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="O5:O404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pilihan tidak valid" error="Silakan pilih dari daftar dropdown." type="list">
-      <formula1>=Daftar!$M$2:$M$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="G16" s="53" t="inlineStr">
         <is>
-          <t>Tertulis</t>
+          <t>Coach Gratis</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
         <v/>
       </c>
       <c r="G17" s="54">
-        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A17,'Kolam Mitra'!$I$5:$I$404,"Tertulis")</f>
+        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A17,'Kolam Mitra'!$J$5:$J$404,"Gratis")</f>
         <v/>
       </c>
     </row>
@@ -13083,7 +13083,7 @@
         <v/>
       </c>
       <c r="G18" s="54">
-        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A18,'Kolam Mitra'!$I$5:$I$404,"Tertulis")</f>
+        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A18,'Kolam Mitra'!$J$5:$J$404,"Gratis")</f>
         <v/>
       </c>
     </row>
@@ -13114,7 +13114,7 @@
         <v/>
       </c>
       <c r="G19" s="54">
-        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A19,'Kolam Mitra'!$I$5:$I$404,"Tertulis")</f>
+        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A19,'Kolam Mitra'!$J$5:$J$404,"Gratis")</f>
         <v/>
       </c>
     </row>
@@ -13145,7 +13145,7 @@
         <v/>
       </c>
       <c r="G20" s="54">
-        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A20,'Kolam Mitra'!$I$5:$I$404,"Tertulis")</f>
+        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A20,'Kolam Mitra'!$J$5:$J$404,"Gratis")</f>
         <v/>
       </c>
     </row>
@@ -13176,7 +13176,7 @@
         <v/>
       </c>
       <c r="G21" s="54">
-        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A21,'Kolam Mitra'!$I$5:$I$404,"Tertulis")</f>
+        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A21,'Kolam Mitra'!$J$5:$J$404,"Gratis")</f>
         <v/>
       </c>
     </row>
@@ -13207,7 +13207,7 @@
         <v/>
       </c>
       <c r="G22" s="54">
-        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A22,'Kolam Mitra'!$I$5:$I$404,"Tertulis")</f>
+        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A22,'Kolam Mitra'!$J$5:$J$404,"Gratis")</f>
         <v/>
       </c>
     </row>
@@ -13238,7 +13238,7 @@
         <v/>
       </c>
       <c r="G23" s="54">
-        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A23,'Kolam Mitra'!$I$5:$I$404,"Tertulis")</f>
+        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A23,'Kolam Mitra'!$J$5:$J$404,"Gratis")</f>
         <v/>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
         <v/>
       </c>
       <c r="G24" s="54">
-        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A24,'Kolam Mitra'!$I$5:$I$404,"Tertulis")</f>
+        <f>COUNTIFS('Kolam Mitra'!$C$5:$C$404,$A24,'Kolam Mitra'!$J$5:$J$404,"Gratis")</f>
         <v/>
       </c>
     </row>
